--- a/static/files/logements_edd.xlsx
+++ b/static/files/logements_edd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA78EC9-74BA-9442-870C-1D90BA0E19B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89936FD8-73E8-7241-B1BA-D16B93F71F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33740" yWindow="3920" windowWidth="27020" windowHeight="16440" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
+    <workbookView xWindow="1000" yWindow="500" windowWidth="27800" windowHeight="17500" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
   <sheets>
     <sheet name="EDD Simplifié" sheetId="1" r:id="rId1"/>
